--- a/Investment data.xlsx
+++ b/Investment data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohan\Desktop\INVESTMENT DASHBOARD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohan\Documents\Dash\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4796693E-0F30-4D7A-8E63-C79C1956935B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E95D73-89EF-4B20-903E-260665D1EF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0FC04731-7B55-48A8-A261-9BB10E86AB45}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0FC04731-7B55-48A8-A261-9BB10E86AB45}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="493">
   <si>
     <t>Sl. No.</t>
   </si>
@@ -662,9 +662,6 @@
 Integrating with smart wearables for proactive care
 Gamified engagement 
 Culturally relevant ,localised language &amp; designed for Indian lifestyle patterns, scalable globally.</t>
-  </si>
-  <si>
-    <t>TRL: 9 for LAM-DED technology and TRL:4 for Micro 3D Printing</t>
   </si>
   <si>
     <t>Strong Backing up by years of research by RRCAT and IIT Indore Proven results across Defence, Space, and Heavy Industries
@@ -1306,9 +1303,6 @@
     <t>Huzur</t>
   </si>
   <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
     <t>Gorakhpur</t>
   </si>
   <si>
@@ -1504,9 +1498,6 @@
     <t>ROORKEE</t>
   </si>
   <si>
-    <t>UTTARAKHAND</t>
-  </si>
-  <si>
     <t>Haridwar</t>
   </si>
   <si>
@@ -1630,12 +1621,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>0.87 Cr</t>
-  </si>
-  <si>
-    <t>3.2 Cr</t>
-  </si>
-  <si>
     <t>3 IPR yet to file</t>
   </si>
   <si>
@@ -1688,6 +1673,9 @@
   </si>
   <si>
     <t>Software+Service+Aggregated Logistics Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRL: 9 </t>
   </si>
 </sst>
 </file>
@@ -2323,20 +2311,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F761443-1744-4535-9313-0EB188E919B2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AH88"/>
-  <sheetFormatPr defaultRowHeight="17.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="17.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="7" width="38.26953125" customWidth="1"/>
-    <col min="8" max="8" width="38.26953125" style="38" customWidth="1"/>
-    <col min="9" max="21" width="38.26953125" customWidth="1"/>
-    <col min="22" max="22" width="38.26953125" style="44" customWidth="1"/>
-    <col min="23" max="26" width="38.26953125" customWidth="1"/>
-    <col min="27" max="27" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="34" width="38.26953125" customWidth="1"/>
-    <col min="35" max="35" width="17.1796875" customWidth="1"/>
+    <col min="1" max="7" width="38.21875" customWidth="1"/>
+    <col min="8" max="8" width="38.21875" style="38" customWidth="1"/>
+    <col min="9" max="21" width="38.21875" customWidth="1"/>
+    <col min="22" max="22" width="38.21875" style="44" customWidth="1"/>
+    <col min="23" max="26" width="38.21875" customWidth="1"/>
+    <col min="27" max="27" width="39.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="34" width="38.21875" customWidth="1"/>
+    <col min="35" max="35" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:34" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2374,73 +2363,73 @@
         <v>158</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="O1" s="26" t="s">
+        <v>321</v>
+      </c>
+      <c r="P1" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="Q1" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="R1" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="S1" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="S1" s="27" t="s">
-        <v>326</v>
-      </c>
       <c r="T1" s="26" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="V1" s="39" t="s">
+        <v>446</v>
+      </c>
+      <c r="W1" s="27" t="s">
+        <v>447</v>
+      </c>
+      <c r="X1" s="27" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y1" s="27" t="s">
         <v>449</v>
       </c>
-      <c r="W1" s="27" t="s">
+      <c r="Z1" s="27" t="s">
         <v>450</v>
       </c>
-      <c r="X1" s="27" t="s">
+      <c r="AA1" s="27" t="s">
         <v>451</v>
       </c>
-      <c r="Y1" s="27" t="s">
+      <c r="AB1" s="27" t="s">
         <v>452</v>
       </c>
-      <c r="Z1" s="27" t="s">
+      <c r="AC1" s="27" t="s">
         <v>453</v>
       </c>
-      <c r="AA1" s="27" t="s">
+      <c r="AD1" s="27" t="s">
         <v>454</v>
       </c>
-      <c r="AB1" s="27" t="s">
+      <c r="AE1" s="27" t="s">
         <v>455</v>
       </c>
-      <c r="AC1" s="27" t="s">
+      <c r="AF1" s="27" t="s">
         <v>456</v>
       </c>
-      <c r="AD1" s="27" t="s">
+      <c r="AG1" s="27" t="s">
         <v>457</v>
       </c>
-      <c r="AE1" s="27" t="s">
+      <c r="AH1" s="27" t="s">
         <v>458</v>
       </c>
-      <c r="AF1" s="27" t="s">
-        <v>459</v>
-      </c>
-      <c r="AG1" s="27" t="s">
-        <v>460</v>
-      </c>
-      <c r="AH1" s="27" t="s">
-        <v>461</v>
-      </c>
     </row>
-    <row r="2" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2478,31 +2467,31 @@
         <v>164</v>
       </c>
       <c r="M2" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="N2" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="N2" s="19" t="s">
-        <v>280</v>
-      </c>
       <c r="O2" s="24" t="s">
+        <v>326</v>
+      </c>
+      <c r="P2" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="R2" s="25" t="s">
         <v>327</v>
       </c>
-      <c r="P2" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="Q2" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="R2" s="25" t="s">
+      <c r="S2" s="25" t="s">
         <v>328</v>
       </c>
-      <c r="S2" s="25" t="s">
-        <v>329</v>
-      </c>
       <c r="T2" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U2" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V2" s="40">
         <v>25.78</v>
@@ -2517,7 +2506,7 @@
         <v>216</v>
       </c>
       <c r="Z2" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA2" s="32">
         <v>14</v>
@@ -2541,10 +2530,10 @@
         <v>1</v>
       </c>
       <c r="AH2" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -2567,7 +2556,7 @@
         <v>166</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>161</v>
@@ -2582,31 +2571,31 @@
         <v>164</v>
       </c>
       <c r="M3" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="N3" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="N3" s="21" t="s">
-        <v>280</v>
-      </c>
       <c r="O3" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q3" s="25" t="s">
         <v>330</v>
       </c>
-      <c r="P3" s="25" t="s">
-        <v>330</v>
-      </c>
-      <c r="Q3" s="25" t="s">
+      <c r="R3" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="R3" s="25" t="s">
+      <c r="S3" s="25" t="s">
         <v>332</v>
       </c>
-      <c r="S3" s="25" t="s">
-        <v>333</v>
-      </c>
       <c r="T3" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U3" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V3" s="40">
         <v>0</v>
@@ -2615,13 +2604,13 @@
         <v>0</v>
       </c>
       <c r="X3" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Y3" s="32">
         <v>10</v>
       </c>
       <c r="Z3" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA3" s="32">
         <v>8</v>
@@ -2645,10 +2634,10 @@
         <v>0</v>
       </c>
       <c r="AH3" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2686,31 +2675,31 @@
         <v>174</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O4" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q4" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q4" s="29" t="s">
+      <c r="R4" s="29" t="s">
         <v>335</v>
       </c>
-      <c r="R4" s="29" t="s">
+      <c r="S4" s="29" t="s">
         <v>336</v>
       </c>
-      <c r="S4" s="29" t="s">
-        <v>337</v>
-      </c>
       <c r="T4" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U4" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V4" s="41">
         <v>1400</v>
@@ -2725,7 +2714,7 @@
         <v>300</v>
       </c>
       <c r="Z4" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA4" s="33">
         <v>60</v>
@@ -2752,7 +2741,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2790,31 +2779,31 @@
         <v>174</v>
       </c>
       <c r="M5" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>283</v>
-      </c>
       <c r="O5" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="P5" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q5" s="29" t="s">
         <v>338</v>
       </c>
-      <c r="P5" s="29" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>339</v>
-      </c>
       <c r="R5" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="S5" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="S5" s="29" t="s">
-        <v>333</v>
-      </c>
       <c r="T5" s="28" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="U5" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V5" s="41">
         <v>57.5</v>
@@ -2829,7 +2818,7 @@
         <v>15000</v>
       </c>
       <c r="Z5" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA5" s="33">
         <v>20</v>
@@ -2853,10 +2842,10 @@
         <v>1</v>
       </c>
       <c r="AH5" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -2894,31 +2883,31 @@
         <v>164</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O6" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="P6" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q6" s="31" t="s">
         <v>340</v>
       </c>
-      <c r="P6" s="31" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q6" s="31" t="s">
-        <v>341</v>
-      </c>
       <c r="R6" s="31" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S6" s="31" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T6" s="30" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U6" s="31" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V6" s="42">
         <v>70</v>
@@ -2933,7 +2922,7 @@
         <v>15</v>
       </c>
       <c r="Z6" s="31" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA6" s="34">
         <v>15</v>
@@ -2957,10 +2946,10 @@
         <v>1</v>
       </c>
       <c r="AH6" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2998,31 +2987,31 @@
         <v>164</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O7" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="P7" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="P7" s="29" t="s">
+      <c r="Q7" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="Q7" s="29" t="s">
-        <v>344</v>
-      </c>
       <c r="R7" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S7" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T7" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U7" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V7" s="41">
         <v>57</v>
@@ -3037,7 +3026,7 @@
         <v>6</v>
       </c>
       <c r="Z7" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA7" s="33">
         <v>13</v>
@@ -3064,7 +3053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3102,37 +3091,37 @@
         <v>174</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O8" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="P8" s="29" t="s">
         <v>345</v>
       </c>
-      <c r="P8" s="29" t="s">
+      <c r="Q8" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="Q8" s="29" t="s">
+      <c r="R8" s="29" t="s">
         <v>347</v>
       </c>
-      <c r="R8" s="29" t="s">
+      <c r="S8" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="S8" s="29" t="s">
-        <v>349</v>
-      </c>
       <c r="T8" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U8" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V8" s="41">
         <v>30</v>
       </c>
       <c r="W8" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="X8" s="33">
         <v>0.26</v>
@@ -3141,7 +3130,7 @@
         <v>9</v>
       </c>
       <c r="Z8" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA8" s="33">
         <v>14</v>
@@ -3165,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="AH8" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -3206,31 +3195,31 @@
         <v>174</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O9" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P9" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q9" s="25" t="s">
         <v>350</v>
       </c>
-      <c r="Q9" s="25" t="s">
+      <c r="R9" s="29" t="s">
         <v>351</v>
       </c>
-      <c r="R9" s="29" t="s">
-        <v>352</v>
-      </c>
       <c r="S9" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T9" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="U9" s="29" t="s">
         <v>442</v>
-      </c>
-      <c r="U9" s="29" t="s">
-        <v>445</v>
       </c>
       <c r="V9" s="41">
         <v>35</v>
@@ -3245,7 +3234,7 @@
         <v>15</v>
       </c>
       <c r="Z9" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA9" s="33">
         <v>46</v>
@@ -3269,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="AH9" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3310,29 +3299,29 @@
         <v>174</v>
       </c>
       <c r="M10" s="22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N10" s="23"/>
       <c r="O10" s="28" t="s">
+        <v>352</v>
+      </c>
+      <c r="P10" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="P10" s="29" t="s">
+      <c r="Q10" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="Q10" s="29" t="s">
-        <v>355</v>
-      </c>
       <c r="R10" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S10" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T10" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U10" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V10" s="41">
         <v>168</v>
@@ -3347,7 +3336,7 @@
         <v>60</v>
       </c>
       <c r="Z10" s="29" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AA10" s="33">
         <v>25</v>
@@ -3356,23 +3345,23 @@
         <v>40</v>
       </c>
       <c r="AC10" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AD10" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AE10" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AF10" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG10" s="33">
         <v>1</v>
       </c>
       <c r="AH10" s="29"/>
     </row>
-    <row r="11" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3410,31 +3399,31 @@
         <v>174</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O11" s="28" t="s">
+        <v>355</v>
+      </c>
+      <c r="P11" s="29" t="s">
         <v>356</v>
       </c>
-      <c r="P11" s="29" t="s">
+      <c r="Q11" s="29" t="s">
         <v>357</v>
       </c>
-      <c r="Q11" s="29" t="s">
+      <c r="R11" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="R11" s="29" t="s">
-        <v>359</v>
-      </c>
       <c r="S11" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T11" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="U11" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V11" s="41">
         <v>160</v>
@@ -3449,7 +3438,7 @@
         <v>22000</v>
       </c>
       <c r="Z11" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA11" s="33">
         <v>30</v>
@@ -3458,25 +3447,25 @@
         <v>25</v>
       </c>
       <c r="AC11" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AD11" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AE11" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF11" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG11" s="33">
         <v>1</v>
       </c>
       <c r="AH11" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6">
         <v>11</v>
       </c>
@@ -3514,31 +3503,31 @@
         <v>174</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q12" s="29" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R12" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S12" s="25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U12" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V12" s="40">
         <v>65</v>
@@ -3553,7 +3542,7 @@
         <v>13000</v>
       </c>
       <c r="Z12" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA12" s="32">
         <v>12</v>
@@ -3575,10 +3564,10 @@
         <v>1</v>
       </c>
       <c r="AH12" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3616,31 +3605,31 @@
         <v>164</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N13" s="4" t="s">
         <v>188</v>
       </c>
       <c r="O13" s="28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P13" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q13" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R13" s="29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S13" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T13" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="U13" s="29" t="s">
         <v>442</v>
-      </c>
-      <c r="U13" s="29" t="s">
-        <v>445</v>
       </c>
       <c r="V13" s="43"/>
       <c r="W13" s="33">
@@ -3653,7 +3642,7 @@
         <v>66</v>
       </c>
       <c r="Z13" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA13" s="33">
         <v>25</v>
@@ -3677,10 +3666,10 @@
         <v>4</v>
       </c>
       <c r="AH13" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3718,31 +3707,31 @@
         <v>174</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O14" s="28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P14" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q14" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S14" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T14" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U14" s="29" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V14" s="43"/>
       <c r="W14" s="33">
@@ -3755,7 +3744,7 @@
         <v>200</v>
       </c>
       <c r="Z14" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA14" s="33">
         <v>4</v>
@@ -3779,10 +3768,10 @@
         <v>0</v>
       </c>
       <c r="AH14" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -3805,7 +3794,7 @@
         <v>191</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>161</v>
@@ -3820,31 +3809,31 @@
         <v>174</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O15" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q15" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="R15" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="S15" s="29" t="s">
         <v>362</v>
       </c>
-      <c r="P15" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="Q15" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="R15" s="29" t="s">
-        <v>336</v>
-      </c>
-      <c r="S15" s="29" t="s">
-        <v>363</v>
-      </c>
       <c r="T15" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U15" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V15" s="41">
         <v>22</v>
@@ -3859,7 +3848,7 @@
         <v>10</v>
       </c>
       <c r="Z15" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA15" s="33">
         <v>0</v>
@@ -3874,10 +3863,10 @@
         <v>2</v>
       </c>
       <c r="AE15" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF15" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG15" s="33">
         <v>1</v>
@@ -3886,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3909,7 +3898,7 @@
         <v>170</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>178</v>
@@ -3924,31 +3913,31 @@
         <v>164</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N16" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O16" s="28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P16" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q16" s="29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R16" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S16" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T16" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U16" s="29" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V16" s="41">
         <v>60</v>
@@ -3963,7 +3952,7 @@
         <v>250</v>
       </c>
       <c r="Z16" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA16" s="33">
         <v>12</v>
@@ -3987,10 +3976,10 @@
         <v>6</v>
       </c>
       <c r="AH16" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -4028,37 +4017,37 @@
         <v>174</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O17" s="24" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P17" s="25" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q17" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R17" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S17" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U17" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V17" s="40">
         <v>50</v>
       </c>
       <c r="W17" s="25" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="X17" s="32">
         <v>0.1</v>
@@ -4067,7 +4056,7 @@
         <v>3</v>
       </c>
       <c r="Z17" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA17" s="32">
         <v>6</v>
@@ -4091,10 +4080,10 @@
         <v>0</v>
       </c>
       <c r="AH17" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -4132,31 +4121,31 @@
         <v>174</v>
       </c>
       <c r="M18" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N18" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O18" s="24" t="s">
+        <v>365</v>
+      </c>
+      <c r="P18" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q18" s="25" t="s">
         <v>366</v>
       </c>
-      <c r="P18" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q18" s="25" t="s">
-        <v>367</v>
-      </c>
       <c r="R18" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S18" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U18" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V18" s="40">
         <v>7</v>
@@ -4171,7 +4160,7 @@
         <v>5</v>
       </c>
       <c r="Z18" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA18" s="32">
         <v>9</v>
@@ -4195,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="AH18" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:34" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -4221,13 +4210,13 @@
         <v>191</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>197</v>
+        <v>492</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>163</v>
@@ -4236,31 +4225,31 @@
         <v>174</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O19" s="24" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P19" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q19" s="25" t="s">
-        <v>339</v>
+        <v>363</v>
+      </c>
+      <c r="Q19" s="29" t="s">
+        <v>338</v>
       </c>
       <c r="R19" s="25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S19" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T19" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U19" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V19" s="40">
         <v>3.5</v>
@@ -4272,10 +4261,10 @@
         <v>0.15</v>
       </c>
       <c r="Y19" s="25" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="Z19" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA19" s="32">
         <v>7</v>
@@ -4284,10 +4273,10 @@
         <v>76</v>
       </c>
       <c r="AC19" s="25" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AD19" s="25" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AE19" s="32">
         <v>1</v>
@@ -4299,10 +4288,10 @@
         <v>1</v>
       </c>
       <c r="AH19" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -4331,7 +4320,7 @@
         <v>178</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>163</v>
@@ -4340,46 +4329,46 @@
         <v>164</v>
       </c>
       <c r="M20" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O20" s="24" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P20" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q20" s="25" t="s">
-        <v>369</v>
+        <v>363</v>
+      </c>
+      <c r="Q20" s="29" t="s">
+        <v>338</v>
       </c>
       <c r="R20" s="25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S20" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T20" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U20" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V20" s="40">
         <v>94.5</v>
       </c>
       <c r="W20" s="25" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="X20" s="25" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="Y20" s="32">
         <v>20</v>
       </c>
       <c r="Z20" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA20" s="32">
         <v>20</v>
@@ -4403,10 +4392,10 @@
         <v>1</v>
       </c>
       <c r="AH20" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -4429,13 +4418,13 @@
         <v>191</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>168</v>
@@ -4444,31 +4433,31 @@
         <v>174</v>
       </c>
       <c r="M21" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="N21" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="N21" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="O21" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P21" s="25" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q21" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R21" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S21" s="25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T21" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U21" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V21" s="40">
         <v>50</v>
@@ -4483,7 +4472,7 @@
         <v>3</v>
       </c>
       <c r="Z21" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA21" s="32">
         <v>4</v>
@@ -4507,10 +4496,10 @@
         <v>0</v>
       </c>
       <c r="AH21" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -4530,16 +4519,16 @@
         <v>165</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>168</v>
@@ -4548,31 +4537,31 @@
         <v>164</v>
       </c>
       <c r="M22" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N22" s="25" t="s">
         <v>169</v>
       </c>
       <c r="O22" s="28" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P22" s="29" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="Q22" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R22" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S22" s="29" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="T22" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U22" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V22" s="41">
         <v>11.25</v>
@@ -4587,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA22" s="33">
         <v>10</v>
@@ -4611,10 +4600,10 @@
         <v>1</v>
       </c>
       <c r="AH22" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -4637,13 +4626,13 @@
         <v>160</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>163</v>
@@ -4652,31 +4641,31 @@
         <v>174</v>
       </c>
       <c r="M23" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="N23" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="N23" s="4" t="s">
-        <v>280</v>
-      </c>
       <c r="O23" s="28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P23" s="29" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q23" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R23" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="S23" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="S23" s="29" t="s">
-        <v>333</v>
-      </c>
       <c r="T23" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U23" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V23" s="41">
         <v>345.46</v>
@@ -4691,7 +4680,7 @@
         <v>200</v>
       </c>
       <c r="Z23" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA23" s="33">
         <v>30</v>
@@ -4703,22 +4692,22 @@
         <v>8</v>
       </c>
       <c r="AD23" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AE23" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AF23" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG23" s="29" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AH23" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -4741,13 +4730,13 @@
         <v>166</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>173</v>
@@ -4756,37 +4745,37 @@
         <v>174</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O24" s="28" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P24" s="29" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="Q24" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R24" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="S24" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="S24" s="29" t="s">
-        <v>333</v>
-      </c>
       <c r="T24" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U24" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V24" s="41">
         <v>178</v>
       </c>
       <c r="W24" s="29" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="X24" s="33">
         <v>0.05</v>
@@ -4795,7 +4784,7 @@
         <v>6</v>
       </c>
       <c r="Z24" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA24" s="33">
         <v>18</v>
@@ -4816,13 +4805,13 @@
         <v>0</v>
       </c>
       <c r="AG24" s="29" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AH24" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -4845,13 +4834,13 @@
         <v>160</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>173</v>
@@ -4860,31 +4849,31 @@
         <v>174</v>
       </c>
       <c r="M25" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O25" s="24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="P25" s="25" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Q25" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="R25" s="25" t="s">
         <v>351</v>
       </c>
-      <c r="R25" s="25" t="s">
-        <v>352</v>
-      </c>
       <c r="S25" s="25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T25" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U25" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V25" s="40">
         <v>487</v>
@@ -4899,7 +4888,7 @@
         <v>17000</v>
       </c>
       <c r="Z25" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA25" s="32">
         <v>20</v>
@@ -4926,7 +4915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -4955,7 +4944,7 @@
         <v>161</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>163</v>
@@ -4964,31 +4953,31 @@
         <v>164</v>
       </c>
       <c r="M26" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N26" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O26" s="24" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="P26" s="25" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="Q26" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R26" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S26" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T26" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U26" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V26" s="40">
         <v>41</v>
@@ -5003,7 +4992,7 @@
         <v>6</v>
       </c>
       <c r="Z26" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA26" s="32">
         <v>12</v>
@@ -5027,10 +5016,10 @@
         <v>1</v>
       </c>
       <c r="AH26" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -5047,19 +5036,19 @@
         <v>149</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>166</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>168</v>
@@ -5068,31 +5057,31 @@
         <v>164</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O27" s="24" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="P27" s="25" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="Q27" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R27" s="25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S27" s="25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T27" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U27" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V27" s="40">
         <v>47</v>
@@ -5107,7 +5096,7 @@
         <v>6</v>
       </c>
       <c r="Z27" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA27" s="32">
         <v>10</v>
@@ -5122,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="AE27" s="25" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AF27" s="32">
         <v>0</v>
@@ -5134,7 +5123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -5163,7 +5152,7 @@
         <v>161</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>163</v>
@@ -5172,37 +5161,37 @@
         <v>164</v>
       </c>
       <c r="M28" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N28" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O28" s="24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="P28" s="25" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q28" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="R28" s="25" t="s">
         <v>331</v>
       </c>
-      <c r="R28" s="25" t="s">
-        <v>332</v>
-      </c>
       <c r="S28" s="25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T28" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U28" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V28" s="40">
         <v>66</v>
       </c>
       <c r="W28" s="25" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="X28" s="32">
         <v>0.15</v>
@@ -5211,7 +5200,7 @@
         <v>10</v>
       </c>
       <c r="Z28" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA28" s="32">
         <v>25</v>
@@ -5220,25 +5209,25 @@
         <v>10</v>
       </c>
       <c r="AC28" s="25" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AD28" s="25" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AE28" s="25" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AF28" s="25" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AG28" s="32">
         <v>1</v>
       </c>
       <c r="AH28" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -5261,13 +5250,13 @@
         <v>180</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>163</v>
@@ -5276,31 +5265,31 @@
         <v>164</v>
       </c>
       <c r="M29" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O29" s="24" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="P29" s="25" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="Q29" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R29" s="25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S29" s="25" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="T29" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U29" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V29" s="40">
         <v>15</v>
@@ -5315,7 +5304,7 @@
         <v>2</v>
       </c>
       <c r="Z29" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA29" s="32">
         <v>5</v>
@@ -5336,13 +5325,13 @@
         <v>4</v>
       </c>
       <c r="AG29" s="25" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AH29" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6">
         <v>29</v>
       </c>
@@ -5371,7 +5360,7 @@
         <v>178</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>173</v>
@@ -5380,46 +5369,46 @@
         <v>164</v>
       </c>
       <c r="M30" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O30" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P30" s="29" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="Q30" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R30" s="29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S30" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T30" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U30" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V30" s="41">
         <v>70</v>
       </c>
-      <c r="W30" s="29" t="s">
-        <v>477</v>
-      </c>
-      <c r="X30" s="29" t="s">
-        <v>478</v>
+      <c r="W30" s="29">
+        <v>0.87</v>
+      </c>
+      <c r="X30" s="29">
+        <v>3.2</v>
       </c>
       <c r="Y30" s="33">
         <v>15</v>
       </c>
       <c r="Z30" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA30" s="33">
         <v>10</v>
@@ -5431,22 +5420,22 @@
         <v>1</v>
       </c>
       <c r="AD30" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AE30" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF30" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG30" s="33">
         <v>1</v>
       </c>
       <c r="AH30" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -5466,16 +5455,16 @@
         <v>169</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>163</v>
@@ -5484,31 +5473,31 @@
         <v>174</v>
       </c>
       <c r="M31" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O31" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="P31" s="29" t="s">
         <v>345</v>
       </c>
-      <c r="P31" s="29" t="s">
+      <c r="Q31" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="Q31" s="29" t="s">
-        <v>347</v>
-      </c>
       <c r="R31" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S31" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T31" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U31" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V31" s="41">
         <v>102</v>
@@ -5523,7 +5512,7 @@
         <v>45000</v>
       </c>
       <c r="Z31" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA31" s="33">
         <v>15</v>
@@ -5547,10 +5536,10 @@
         <v>0</v>
       </c>
       <c r="AH31" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -5579,7 +5568,7 @@
         <v>161</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>163</v>
@@ -5588,31 +5577,31 @@
         <v>174</v>
       </c>
       <c r="M32" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N32" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O32" s="24" t="s">
+        <v>377</v>
+      </c>
+      <c r="P32" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q32" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="P32" s="25" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q32" s="25" t="s">
-        <v>381</v>
-      </c>
       <c r="R32" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S32" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T32" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U32" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V32" s="40">
         <v>110</v>
@@ -5627,7 +5616,7 @@
         <v>420</v>
       </c>
       <c r="Z32" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA32" s="32">
         <v>14</v>
@@ -5636,7 +5625,7 @@
         <v>26.1</v>
       </c>
       <c r="AC32" s="25" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="AD32" s="32">
         <v>0</v>
@@ -5651,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="AH32" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -5683,7 +5672,7 @@
         <v>178</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>173</v>
@@ -5692,31 +5681,31 @@
         <v>174</v>
       </c>
       <c r="M33" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N33" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O33" s="28" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="P33" s="29" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Q33" s="29" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="R33" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S33" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T33" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U33" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V33" s="41">
         <v>207</v>
@@ -5731,7 +5720,7 @@
         <v>13466</v>
       </c>
       <c r="Z33" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA33" s="33">
         <v>32</v>
@@ -5740,25 +5729,25 @@
         <v>30</v>
       </c>
       <c r="AC33" s="29" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AD33" s="29" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AE33" s="29" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AF33" s="29" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AG33" s="29" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="AH33" s="29" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -5787,7 +5776,7 @@
         <v>161</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>163</v>
@@ -5796,31 +5785,31 @@
         <v>164</v>
       </c>
       <c r="M34" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N34" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O34" s="28" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="P34" s="29" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q34" s="29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R34" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S34" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T34" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U34" s="29" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V34" s="41">
         <v>134</v>
@@ -5835,7 +5824,7 @@
         <v>15</v>
       </c>
       <c r="Z34" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA34" s="33">
         <v>25</v>
@@ -5859,10 +5848,10 @@
         <v>1</v>
       </c>
       <c r="AH34" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -5885,13 +5874,13 @@
         <v>166</v>
       </c>
       <c r="H35" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>163</v>
@@ -5900,46 +5889,46 @@
         <v>174</v>
       </c>
       <c r="M35" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O35" s="28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P35" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q35" s="29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R35" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S35" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T35" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U35" s="29" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="V35" s="41">
         <v>90</v>
       </c>
       <c r="W35" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X35" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="Y35" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="Z35" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA35" s="33">
         <v>500</v>
@@ -5963,10 +5952,10 @@
         <v>10</v>
       </c>
       <c r="AH35" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -5989,13 +5978,13 @@
         <v>170</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>163</v>
@@ -6004,31 +5993,31 @@
         <v>174</v>
       </c>
       <c r="M36" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O36" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P36" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q36" s="29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="R36" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S36" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T36" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U36" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V36" s="41">
         <v>175</v>
@@ -6041,7 +6030,7 @@
         <v>27500</v>
       </c>
       <c r="Z36" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA36" s="33">
         <v>17</v>
@@ -6050,25 +6039,25 @@
         <v>37.433999999999997</v>
       </c>
       <c r="AC36" s="29" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AD36" s="29" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AE36" s="29" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AF36" s="29" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AG36" s="29" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="AH36" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -6097,7 +6086,7 @@
         <v>178</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>163</v>
@@ -6106,31 +6095,31 @@
         <v>174</v>
       </c>
       <c r="M37" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N37" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O37" s="24" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P37" s="25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q37" s="25" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="R37" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S37" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T37" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="U37" s="25" t="s">
         <v>442</v>
-      </c>
-      <c r="U37" s="25" t="s">
-        <v>445</v>
       </c>
       <c r="V37" s="40">
         <v>68</v>
@@ -6145,7 +6134,7 @@
         <v>26</v>
       </c>
       <c r="Z37" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA37" s="32">
         <v>8</v>
@@ -6169,10 +6158,10 @@
         <v>1</v>
       </c>
       <c r="AH37" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -6201,7 +6190,7 @@
         <v>178</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>163</v>
@@ -6210,31 +6199,31 @@
         <v>174</v>
       </c>
       <c r="M38" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N38" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O38" s="28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P38" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q38" s="29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R38" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S38" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T38" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U38" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V38" s="41">
         <v>68.5</v>
@@ -6243,13 +6232,13 @@
         <v>0.03</v>
       </c>
       <c r="X38" s="29" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="Y38" s="33">
         <v>6</v>
       </c>
       <c r="Z38" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA38" s="33">
         <v>5</v>
@@ -6273,10 +6262,10 @@
         <v>0</v>
       </c>
       <c r="AH38" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -6305,7 +6294,7 @@
         <v>178</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>168</v>
@@ -6314,31 +6303,31 @@
         <v>164</v>
       </c>
       <c r="M39" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N39" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O39" s="28" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="P39" s="29" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Q39" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R39" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S39" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T39" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U39" s="29" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V39" s="41">
         <v>35</v>
@@ -6353,13 +6342,13 @@
         <v>12789</v>
       </c>
       <c r="Z39" s="29" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AA39" s="33">
         <v>59</v>
       </c>
       <c r="AB39" s="29" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AC39" s="33">
         <v>0</v>
@@ -6377,10 +6366,10 @@
         <v>1</v>
       </c>
       <c r="AH39" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -6409,7 +6398,7 @@
         <v>161</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>163</v>
@@ -6418,31 +6407,31 @@
         <v>164</v>
       </c>
       <c r="M40" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N40" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O40" s="28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="P40" s="29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q40" s="29" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R40" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S40" s="29" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T40" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U40" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V40" s="41">
         <v>10</v>
@@ -6455,7 +6444,7 @@
         <v>20000</v>
       </c>
       <c r="Z40" s="29" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AA40" s="33">
         <v>8</v>
@@ -6479,10 +6468,10 @@
         <v>2</v>
       </c>
       <c r="AH40" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -6505,13 +6494,13 @@
         <v>180</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>168</v>
@@ -6520,31 +6509,31 @@
         <v>164</v>
       </c>
       <c r="M41" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O41" s="28" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="P41" s="29" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Q41" s="29" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="R41" s="29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S41" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T41" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U41" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V41" s="41">
         <v>150</v>
@@ -6557,7 +6546,7 @@
         <v>4</v>
       </c>
       <c r="Z41" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA41" s="33">
         <v>37</v>
@@ -6584,7 +6573,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="6">
         <v>41</v>
       </c>
@@ -6613,7 +6602,7 @@
         <v>161</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>173</v>
@@ -6622,31 +6611,31 @@
         <v>164</v>
       </c>
       <c r="M42" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O42" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="P42" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="P42" s="25" t="s">
+      <c r="Q42" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="Q42" s="29" t="s">
-        <v>347</v>
-      </c>
       <c r="R42" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S42" s="25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T42" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U42" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V42" s="40">
         <v>735</v>
@@ -6661,7 +6650,7 @@
         <v>69204</v>
       </c>
       <c r="Z42" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA42" s="32">
         <v>32</v>
@@ -6685,10 +6674,10 @@
         <v>6</v>
       </c>
       <c r="AH42" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -6708,7 +6697,7 @@
         <v>169</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H43" s="13" t="s">
         <v>182</v>
@@ -6717,7 +6706,7 @@
         <v>161</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>163</v>
@@ -6726,31 +6715,31 @@
         <v>174</v>
       </c>
       <c r="M43" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N43" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O43" s="24" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P43" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="Q43" s="25" t="s">
-        <v>339</v>
+        <v>388</v>
+      </c>
+      <c r="Q43" s="29" t="s">
+        <v>338</v>
       </c>
       <c r="R43" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="S43" s="25" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="T43" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U43" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V43" s="40">
         <v>58.4</v>
@@ -6765,7 +6754,7 @@
         <v>2500</v>
       </c>
       <c r="Z43" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA43" s="32">
         <v>17</v>
@@ -6789,10 +6778,10 @@
         <v>2</v>
       </c>
       <c r="AH43" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -6821,7 +6810,7 @@
         <v>161</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>163</v>
@@ -6830,31 +6819,31 @@
         <v>164</v>
       </c>
       <c r="M44" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O44" s="28" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="P44" s="29" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q44" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R44" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S44" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T44" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U44" s="29" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="V44" s="41">
         <v>80</v>
@@ -6869,7 +6858,7 @@
         <v>14</v>
       </c>
       <c r="Z44" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA44" s="33">
         <v>40</v>
@@ -6896,7 +6885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -6925,7 +6914,7 @@
         <v>161</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>163</v>
@@ -6934,31 +6923,31 @@
         <v>164</v>
       </c>
       <c r="M45" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="N45" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="N45" s="4" t="s">
-        <v>280</v>
-      </c>
       <c r="O45" s="28" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="P45" s="29" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q45" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="R45" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="R45" s="29" t="s">
-        <v>332</v>
-      </c>
       <c r="S45" s="29" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T45" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U45" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V45" s="41">
         <v>13</v>
@@ -6973,7 +6962,7 @@
         <v>5</v>
       </c>
       <c r="Z45" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA45" s="33">
         <v>10</v>
@@ -6997,10 +6986,10 @@
         <v>2</v>
       </c>
       <c r="AH45" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -7029,7 +7018,7 @@
         <v>161</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>168</v>
@@ -7038,31 +7027,31 @@
         <v>164</v>
       </c>
       <c r="M46" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O46" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="P46" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q46" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="P46" s="25" t="s">
-        <v>396</v>
-      </c>
-      <c r="Q46" s="25" t="s">
-        <v>397</v>
-      </c>
       <c r="R46" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S46" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T46" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U46" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V46" s="40">
         <v>21.5</v>
@@ -7071,13 +7060,13 @@
         <v>0</v>
       </c>
       <c r="X46" s="25" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="Y46" s="32">
         <v>2</v>
       </c>
       <c r="Z46" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA46" s="32">
         <v>30</v>
@@ -7101,10 +7090,10 @@
         <v>1</v>
       </c>
       <c r="AH46" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="47" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -7133,7 +7122,7 @@
         <v>178</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>168</v>
@@ -7142,31 +7131,31 @@
         <v>164</v>
       </c>
       <c r="M47" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O47" s="24" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="P47" s="25" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Q47" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R47" s="25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S47" s="25" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T47" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="U47" s="25" t="s">
         <v>442</v>
-      </c>
-      <c r="U47" s="25" t="s">
-        <v>445</v>
       </c>
       <c r="V47" s="40">
         <v>20</v>
@@ -7181,7 +7170,7 @@
         <v>4</v>
       </c>
       <c r="Z47" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA47" s="32">
         <v>11</v>
@@ -7205,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AH47" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="6">
         <v>47</v>
       </c>
@@ -7231,13 +7220,13 @@
         <v>166</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>168</v>
@@ -7246,31 +7235,31 @@
         <v>174</v>
       </c>
       <c r="M48" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="O48" s="24" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P48" s="25" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q48" s="25" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="R48" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="S48" s="25" t="s">
         <v>332</v>
       </c>
-      <c r="S48" s="25" t="s">
-        <v>333</v>
-      </c>
       <c r="T48" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="U48" s="25" t="s">
         <v>442</v>
-      </c>
-      <c r="U48" s="25" t="s">
-        <v>445</v>
       </c>
       <c r="V48" s="40">
         <v>2</v>
@@ -7285,7 +7274,7 @@
         <v>5</v>
       </c>
       <c r="Z48" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA48" s="32">
         <v>4</v>
@@ -7309,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="AH48" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -7341,7 +7330,7 @@
         <v>161</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>168</v>
@@ -7350,31 +7339,31 @@
         <v>174</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O49" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="P49" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q49" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="P49" s="29" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q49" s="29" t="s">
-        <v>404</v>
-      </c>
       <c r="R49" s="29" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S49" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T49" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="U49" s="29" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V49" s="41">
         <v>0</v>
@@ -7389,7 +7378,7 @@
         <v>5</v>
       </c>
       <c r="Z49" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA49" s="33">
         <v>5</v>
@@ -7413,10 +7402,10 @@
         <v>0</v>
       </c>
       <c r="AH49" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="50" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -7445,7 +7434,7 @@
         <v>178</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>173</v>
@@ -7454,31 +7443,31 @@
         <v>174</v>
       </c>
       <c r="M50" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N50" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O50" s="24" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P50" s="25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q50" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R50" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S50" s="25" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T50" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U50" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V50" s="40">
         <v>1.25</v>
@@ -7493,7 +7482,7 @@
         <v>5</v>
       </c>
       <c r="Z50" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA50" s="32">
         <v>12</v>
@@ -7517,10 +7506,10 @@
         <v>0</v>
       </c>
       <c r="AH50" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="51" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -7537,7 +7526,7 @@
         <v>151</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>191</v>
@@ -7549,7 +7538,7 @@
         <v>161</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>168</v>
@@ -7558,31 +7547,31 @@
         <v>174</v>
       </c>
       <c r="M51" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="O51" s="28" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="P51" s="29" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="Q51" s="29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="R51" s="29" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S51" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T51" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U51" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V51" s="41">
         <v>52</v>
@@ -7597,7 +7586,7 @@
         <v>2</v>
       </c>
       <c r="Z51" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA51" s="33">
         <v>22</v>
@@ -7621,10 +7610,10 @@
         <v>1</v>
       </c>
       <c r="AH51" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="52" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -7653,7 +7642,7 @@
         <v>178</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>173</v>
@@ -7662,31 +7651,31 @@
         <v>174</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N52" s="4" t="s">
         <v>159</v>
       </c>
       <c r="O52" s="24" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="P52" s="25" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="Q52" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R52" s="25" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="S52" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T52" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U52" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V52" s="40">
         <v>70</v>
@@ -7701,7 +7690,7 @@
         <v>5</v>
       </c>
       <c r="Z52" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA52" s="32">
         <v>8</v>
@@ -7725,10 +7714,10 @@
         <v>1</v>
       </c>
       <c r="AH52" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="53" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -7757,7 +7746,7 @@
         <v>161</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>163</v>
@@ -7766,31 +7755,31 @@
         <v>164</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="O53" s="28" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="P53" s="29" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Q53" s="29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R53" s="29" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="S53" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T53" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U53" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V53" s="41">
         <v>2.62</v>
@@ -7805,7 +7794,7 @@
         <v>5</v>
       </c>
       <c r="Z53" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA53" s="33">
         <v>2</v>
@@ -7829,10 +7818,10 @@
         <v>2</v>
       </c>
       <c r="AH53" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="54" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -7861,7 +7850,7 @@
         <v>161</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>163</v>
@@ -7870,31 +7859,31 @@
         <v>174</v>
       </c>
       <c r="M54" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N54" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O54" s="24" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="P54" s="25" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q54" s="25" t="s">
-        <v>339</v>
+        <v>410</v>
+      </c>
+      <c r="Q54" s="29" t="s">
+        <v>338</v>
       </c>
       <c r="R54" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S54" s="25" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T54" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U54" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V54" s="40">
         <v>144</v>
@@ -7909,7 +7898,7 @@
         <v>5</v>
       </c>
       <c r="Z54" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA54" s="32">
         <v>34</v>
@@ -7933,10 +7922,10 @@
         <v>0</v>
       </c>
       <c r="AH54" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="55" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -7965,7 +7954,7 @@
         <v>161</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>163</v>
@@ -7974,31 +7963,31 @@
         <v>174</v>
       </c>
       <c r="M55" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O55" s="28" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="P55" s="29" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Q55" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R55" s="29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S55" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T55" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U55" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V55" s="41">
         <v>43</v>
@@ -8013,7 +8002,7 @@
         <v>400</v>
       </c>
       <c r="Z55" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA55" s="33">
         <v>50</v>
@@ -8037,10 +8026,10 @@
         <v>1</v>
       </c>
       <c r="AH55" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="56" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -8069,7 +8058,7 @@
         <v>161</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>163</v>
@@ -8078,31 +8067,31 @@
         <v>174</v>
       </c>
       <c r="M56" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N56" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O56" s="24" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="P56" s="25" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="Q56" s="25" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="R56" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S56" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T56" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U56" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V56" s="40">
         <v>30</v>
@@ -8117,7 +8106,7 @@
         <v>3000</v>
       </c>
       <c r="Z56" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA56" s="32">
         <v>17</v>
@@ -8141,10 +8130,10 @@
         <v>1</v>
       </c>
       <c r="AH56" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="57" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -8173,7 +8162,7 @@
         <v>178</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>168</v>
@@ -8182,46 +8171,46 @@
         <v>164</v>
       </c>
       <c r="M57" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O57" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="P57" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q57" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="P57" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q57" s="25" t="s">
-        <v>341</v>
-      </c>
       <c r="R57" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S57" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T57" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U57" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V57" s="40">
         <v>24</v>
       </c>
       <c r="W57" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X57" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="Y57" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="Z57" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA57" s="32">
         <v>5</v>
@@ -8245,10 +8234,10 @@
         <v>1</v>
       </c>
       <c r="AH57" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="58" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -8277,7 +8266,7 @@
         <v>178</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>163</v>
@@ -8286,31 +8275,31 @@
         <v>174</v>
       </c>
       <c r="M58" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="O58" s="24" t="s">
+        <v>339</v>
+      </c>
+      <c r="P58" s="25" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q58" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="P58" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q58" s="25" t="s">
-        <v>341</v>
-      </c>
       <c r="R58" s="25" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="S58" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T58" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U58" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V58" s="40">
         <v>45</v>
@@ -8325,7 +8314,7 @@
         <v>119</v>
       </c>
       <c r="Z58" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA58" s="32">
         <v>8</v>
@@ -8337,22 +8326,22 @@
         <v>4</v>
       </c>
       <c r="AD58" s="25" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AE58" s="32">
         <v>1</v>
       </c>
       <c r="AF58" s="25" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG58" s="32">
         <v>3</v>
       </c>
       <c r="AH58" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="59" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -8375,13 +8364,13 @@
         <v>166</v>
       </c>
       <c r="H59" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>163</v>
@@ -8390,31 +8379,31 @@
         <v>174</v>
       </c>
       <c r="M59" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N59" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O59" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="P59" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q59" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="P59" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q59" s="29" t="s">
-        <v>335</v>
-      </c>
       <c r="R59" s="29" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="S59" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T59" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U59" s="29" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V59" s="41">
         <v>160</v>
@@ -8429,7 +8418,7 @@
         <v>25</v>
       </c>
       <c r="Z59" s="29" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA59" s="33">
         <v>45</v>
@@ -8453,10 +8442,10 @@
         <v>0</v>
       </c>
       <c r="AH59" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="60" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="6">
         <v>59</v>
       </c>
@@ -8479,13 +8468,13 @@
         <v>191</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>161</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>168</v>
@@ -8494,31 +8483,31 @@
         <v>164</v>
       </c>
       <c r="M60" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O60" s="28" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="P60" s="29" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="Q60" s="29" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="R60" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S60" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T60" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U60" s="29" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="V60" s="41">
         <v>45</v>
@@ -8533,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="Z60" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA60" s="33">
         <v>5</v>
@@ -8557,10 +8546,10 @@
         <v>0</v>
       </c>
       <c r="AH60" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="61" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -8589,7 +8578,7 @@
         <v>178</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>173</v>
@@ -8598,31 +8587,31 @@
         <v>174</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O61" s="24" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="P61" s="25" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Q61" s="25" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="R61" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S61" s="25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T61" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="U61" s="25" t="s">
         <v>442</v>
-      </c>
-      <c r="U61" s="25" t="s">
-        <v>445</v>
       </c>
       <c r="V61" s="40">
         <v>2</v>
@@ -8637,7 +8626,7 @@
         <v>5</v>
       </c>
       <c r="Z61" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA61" s="32">
         <v>3</v>
@@ -8652,19 +8641,19 @@
         <v>1</v>
       </c>
       <c r="AE61" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF61" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG61" s="32">
         <v>1</v>
       </c>
       <c r="AH61" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="62" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -8684,7 +8673,7 @@
         <v>165</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H62" s="13" t="s">
         <v>182</v>
@@ -8693,7 +8682,7 @@
         <v>178</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>163</v>
@@ -8702,31 +8691,31 @@
         <v>164</v>
       </c>
       <c r="M62" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O62" s="24" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P62" s="25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q62" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="R62" s="25" t="s">
         <v>347</v>
       </c>
-      <c r="R62" s="25" t="s">
+      <c r="S62" s="25" t="s">
         <v>348</v>
       </c>
-      <c r="S62" s="25" t="s">
-        <v>349</v>
-      </c>
       <c r="T62" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U62" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V62" s="40">
         <v>11.25</v>
@@ -8741,7 +8730,7 @@
         <v>205</v>
       </c>
       <c r="Z62" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA62" s="32">
         <v>19</v>
@@ -8765,10 +8754,10 @@
         <v>1</v>
       </c>
       <c r="AH62" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="63" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -8791,13 +8780,13 @@
         <v>180</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>168</v>
@@ -8806,31 +8795,31 @@
         <v>174</v>
       </c>
       <c r="M63" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O63" s="28" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="P63" s="29" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="Q63" s="29" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R63" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S63" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T63" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U63" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V63" s="41">
         <v>10</v>
@@ -8845,7 +8834,7 @@
         <v>5</v>
       </c>
       <c r="Z63" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA63" s="33">
         <v>10</v>
@@ -8854,13 +8843,13 @@
         <v>25</v>
       </c>
       <c r="AC63" s="29" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AD63" s="33">
         <v>0</v>
       </c>
       <c r="AE63" s="29" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AF63" s="33">
         <v>0</v>
@@ -8869,10 +8858,10 @@
         <v>0</v>
       </c>
       <c r="AH63" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="64" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -8895,13 +8884,13 @@
         <v>166</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K64" s="4" t="s">
         <v>168</v>
@@ -8910,46 +8899,46 @@
         <v>164</v>
       </c>
       <c r="M64" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O64" s="24" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="P64" s="25" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="Q64" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R64" s="25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S64" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T64" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U64" s="25" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="V64" s="40">
         <v>37</v>
       </c>
       <c r="W64" s="25" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="X64" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Y64" s="25" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="Z64" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA64" s="32">
         <v>8</v>
@@ -8961,7 +8950,7 @@
         <v>1</v>
       </c>
       <c r="AD64" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AE64" s="32">
         <v>1</v>
@@ -8973,10 +8962,10 @@
         <v>1</v>
       </c>
       <c r="AH64" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="65" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -8999,13 +8988,13 @@
         <v>194</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>168</v>
@@ -9014,46 +9003,46 @@
         <v>164</v>
       </c>
       <c r="M65" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N65" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O65" s="28" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P65" s="29" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Q65" s="29" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R65" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S65" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T65" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="U65" s="29" t="s">
         <v>442</v>
-      </c>
-      <c r="U65" s="29" t="s">
-        <v>445</v>
       </c>
       <c r="V65" s="41">
         <v>76</v>
       </c>
       <c r="W65" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="X65" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="Y65" s="33">
         <v>1</v>
       </c>
       <c r="Z65" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA65" s="33">
         <v>4</v>
@@ -9077,10 +9066,10 @@
         <v>1</v>
       </c>
       <c r="AH65" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="66" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="6">
         <v>65</v>
       </c>
@@ -9103,13 +9092,13 @@
         <v>170</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>168</v>
@@ -9118,31 +9107,31 @@
         <v>164</v>
       </c>
       <c r="M66" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O66" s="24" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="P66" s="25" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="Q66" s="29" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R66" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S66" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T66" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U66" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V66" s="40">
         <v>28</v>
@@ -9157,7 +9146,7 @@
         <v>20</v>
       </c>
       <c r="Z66" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA66" s="32">
         <v>5</v>
@@ -9181,10 +9170,10 @@
         <v>1</v>
       </c>
       <c r="AH66" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="67" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -9207,13 +9196,13 @@
         <v>170</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>173</v>
@@ -9222,31 +9211,31 @@
         <v>164</v>
       </c>
       <c r="M67" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O67" s="24" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="P67" s="25" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Q67" s="25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R67" s="25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S67" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T67" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="U67" s="25" t="s">
         <v>442</v>
-      </c>
-      <c r="U67" s="25" t="s">
-        <v>445</v>
       </c>
       <c r="V67" s="40">
         <v>63</v>
@@ -9261,7 +9250,7 @@
         <v>3300</v>
       </c>
       <c r="Z67" s="25" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AA67" s="32">
         <v>4</v>
@@ -9288,7 +9277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -9311,13 +9300,13 @@
         <v>180</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>173</v>
@@ -9326,31 +9315,31 @@
         <v>164</v>
       </c>
       <c r="M68" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O68" s="28" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="P68" s="29" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q68" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="R68" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="R68" s="29" t="s">
-        <v>332</v>
-      </c>
       <c r="S68" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T68" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U68" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V68" s="41">
         <v>100</v>
@@ -9365,7 +9354,7 @@
         <v>10</v>
       </c>
       <c r="Z68" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA68" s="33">
         <v>25</v>
@@ -9389,10 +9378,10 @@
         <v>1</v>
       </c>
       <c r="AH68" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="69" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -9421,7 +9410,7 @@
         <v>178</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>163</v>
@@ -9430,31 +9419,31 @@
         <v>164</v>
       </c>
       <c r="M69" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N69" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O69" s="24" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="P69" s="25" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="Q69" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R69" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S69" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T69" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U69" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V69" s="40">
         <v>700</v>
@@ -9469,7 +9458,7 @@
         <v>6</v>
       </c>
       <c r="Z69" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA69" s="32">
         <v>18</v>
@@ -9493,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AH69" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="70" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -9525,7 +9514,7 @@
         <v>178</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K70" s="7" t="s">
         <v>163</v>
@@ -9534,31 +9523,31 @@
         <v>174</v>
       </c>
       <c r="M70" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="O70" s="28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P70" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q70" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R70" s="29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="S70" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T70" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U70" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V70" s="41">
         <v>50</v>
@@ -9573,7 +9562,7 @@
         <v>310</v>
       </c>
       <c r="Z70" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA70" s="33">
         <v>14</v>
@@ -9597,10 +9586,10 @@
         <v>174</v>
       </c>
       <c r="AH70" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="71" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -9629,7 +9618,7 @@
         <v>161</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>163</v>
@@ -9638,31 +9627,31 @@
         <v>174</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O71" s="24" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P71" s="25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q71" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R71" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S71" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T71" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U71" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V71" s="40">
         <v>50</v>
@@ -9677,7 +9666,7 @@
         <v>5</v>
       </c>
       <c r="Z71" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA71" s="32">
         <v>8</v>
@@ -9692,7 +9681,7 @@
         <v>1</v>
       </c>
       <c r="AE71" s="25" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="AF71" s="32">
         <v>0</v>
@@ -9701,10 +9690,10 @@
         <v>1</v>
       </c>
       <c r="AH71" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="72" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="6">
         <v>71</v>
       </c>
@@ -9733,7 +9722,7 @@
         <v>161</v>
       </c>
       <c r="J72" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K72" s="7" t="s">
         <v>163</v>
@@ -9742,31 +9731,31 @@
         <v>164</v>
       </c>
       <c r="M72" s="10" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N72" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O72" s="28" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="P72" s="29" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="Q72" s="29" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="R72" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="S72" s="29" t="s">
         <v>328</v>
       </c>
-      <c r="S72" s="29" t="s">
-        <v>329</v>
-      </c>
       <c r="T72" s="28" t="s">
+        <v>439</v>
+      </c>
+      <c r="U72" s="29" t="s">
         <v>442</v>
-      </c>
-      <c r="U72" s="29" t="s">
-        <v>445</v>
       </c>
       <c r="V72" s="41">
         <v>84.93</v>
@@ -9781,7 +9770,7 @@
         <v>450</v>
       </c>
       <c r="Z72" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA72" s="33">
         <v>20</v>
@@ -9808,7 +9797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -9837,7 +9826,7 @@
         <v>161</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>168</v>
@@ -9846,31 +9835,31 @@
         <v>174</v>
       </c>
       <c r="M73" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N73" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O73" s="24" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="P73" s="25" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="Q73" s="25" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="R73" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S73" s="25" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T73" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U73" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V73" s="40">
         <v>92</v>
@@ -9885,7 +9874,7 @@
         <v>75000</v>
       </c>
       <c r="Z73" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA73" s="32">
         <v>8</v>
@@ -9894,25 +9883,25 @@
         <v>30</v>
       </c>
       <c r="AC73" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AD73" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AE73" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF73" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG73" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AH73" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="74" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -9932,7 +9921,7 @@
         <v>165</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H74" s="13" t="s">
         <v>171</v>
@@ -9941,7 +9930,7 @@
         <v>161</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>168</v>
@@ -9950,46 +9939,46 @@
         <v>174</v>
       </c>
       <c r="M74" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N74" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O74" s="24" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="P74" s="25" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Q74" s="25" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="R74" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S74" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T74" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U74" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V74" s="40">
         <v>220</v>
       </c>
       <c r="W74" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X74" s="25" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="Y74" s="32">
         <v>10000</v>
       </c>
       <c r="Z74" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA74" s="32">
         <v>10</v>
@@ -9998,25 +9987,25 @@
         <v>75</v>
       </c>
       <c r="AC74" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AD74" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AE74" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AF74" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AG74" s="25" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AH74" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="75" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="6">
         <v>74</v>
       </c>
@@ -10033,19 +10022,19 @@
         <v>149</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>191</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>168</v>
@@ -10054,31 +10043,31 @@
         <v>164</v>
       </c>
       <c r="M75" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N75" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O75" s="28" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="P75" s="29" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="Q75" s="29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="R75" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S75" s="29" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="T75" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U75" s="29" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="V75" s="41">
         <v>269.39999999999998</v>
@@ -10093,10 +10082,10 @@
         <v>2</v>
       </c>
       <c r="Z75" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA75" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AB75" s="33">
         <v>22</v>
@@ -10117,10 +10106,10 @@
         <v>1</v>
       </c>
       <c r="AH75" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="76" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -10149,7 +10138,7 @@
         <v>161</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>163</v>
@@ -10158,31 +10147,31 @@
         <v>164</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N76" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O76" s="28" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="P76" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q76" s="29" t="s">
         <v>357</v>
       </c>
-      <c r="Q76" s="29" t="s">
-        <v>358</v>
-      </c>
       <c r="R76" s="29" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="S76" s="29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T76" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U76" s="29" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="V76" s="41">
         <v>65</v>
@@ -10197,7 +10186,7 @@
         <v>3</v>
       </c>
       <c r="Z76" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA76" s="33">
         <v>4</v>
@@ -10221,10 +10210,10 @@
         <v>0</v>
       </c>
       <c r="AH76" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="77" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -10244,16 +10233,16 @@
         <v>165</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H77" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>178</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>168</v>
@@ -10262,31 +10251,31 @@
         <v>174</v>
       </c>
       <c r="M77" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N77" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O77" s="28" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P77" s="29" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q77" s="29" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="R77" s="29" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="S77" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T77" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U77" s="29" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V77" s="41">
         <v>60</v>
@@ -10295,19 +10284,19 @@
         <v>0</v>
       </c>
       <c r="X77" s="29" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="Y77" s="33">
         <v>5</v>
       </c>
       <c r="Z77" s="29" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AA77" s="33">
         <v>6</v>
       </c>
       <c r="AB77" s="29" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AC77" s="33">
         <v>0</v>
@@ -10325,10 +10314,10 @@
         <v>0</v>
       </c>
       <c r="AH77" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="78" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6">
         <v>77</v>
       </c>
@@ -10357,7 +10346,7 @@
         <v>161</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>173</v>
@@ -10366,31 +10355,31 @@
         <v>174</v>
       </c>
       <c r="M78" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N78" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O78" s="28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="P78" s="29" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q78" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R78" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S78" s="29" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T78" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U78" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V78" s="41">
         <v>60</v>
@@ -10405,7 +10394,7 @@
         <v>45</v>
       </c>
       <c r="Z78" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA78" s="33">
         <v>11</v>
@@ -10414,25 +10403,25 @@
         <v>15</v>
       </c>
       <c r="AC78" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AD78" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AE78" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AF78" s="29" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AG78" s="33">
         <v>1</v>
       </c>
       <c r="AH78" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="79" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -10461,7 +10450,7 @@
         <v>161</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>173</v>
@@ -10470,31 +10459,31 @@
         <v>164</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N79" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O79" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="P79" s="29" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q79" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="P79" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q79" s="29" t="s">
-        <v>347</v>
-      </c>
       <c r="R79" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S79" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T79" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U79" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V79" s="41">
         <v>25</v>
@@ -10509,7 +10498,7 @@
         <v>1500</v>
       </c>
       <c r="Z79" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA79" s="33">
         <v>42</v>
@@ -10533,10 +10522,10 @@
         <v>0</v>
       </c>
       <c r="AH79" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="80" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -10565,7 +10554,7 @@
         <v>161</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>163</v>
@@ -10574,31 +10563,31 @@
         <v>174</v>
       </c>
       <c r="M80" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N80" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="O80" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="P80" s="25" t="s">
+        <v>415</v>
+      </c>
+      <c r="Q80" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="R80" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="S80" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="T80" s="24" t="s">
         <v>293</v>
       </c>
-      <c r="O80" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="P80" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q80" s="25" t="s">
-        <v>397</v>
-      </c>
-      <c r="R80" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="S80" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="T80" s="24" t="s">
-        <v>294</v>
-      </c>
       <c r="U80" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V80" s="40">
         <v>104</v>
@@ -10613,7 +10602,7 @@
         <v>3000</v>
       </c>
       <c r="Z80" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA80" s="32">
         <v>8</v>
@@ -10637,10 +10626,10 @@
         <v>0</v>
       </c>
       <c r="AH80" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="81" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="6">
         <v>80</v>
       </c>
@@ -10669,7 +10658,7 @@
         <v>161</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K81" s="8" t="s">
         <v>163</v>
@@ -10678,31 +10667,31 @@
         <v>164</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N81" s="7" t="s">
         <v>169</v>
       </c>
       <c r="O81" s="24" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="P81" s="25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="Q81" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R81" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S81" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T81" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U81" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V81" s="40">
         <v>43</v>
@@ -10717,7 +10706,7 @@
         <v>13000</v>
       </c>
       <c r="Z81" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA81" s="32">
         <v>617</v>
@@ -10741,10 +10730,10 @@
         <v>1</v>
       </c>
       <c r="AH81" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="82" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -10764,7 +10753,7 @@
         <v>165</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H82" s="15" t="s">
         <v>182</v>
@@ -10773,7 +10762,7 @@
         <v>178</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K82" s="5" t="s">
         <v>163</v>
@@ -10782,37 +10771,37 @@
         <v>164</v>
       </c>
       <c r="M82" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N82" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O82" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="P82" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="P82" s="25" t="s">
+      <c r="Q82" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="Q82" s="29" t="s">
-        <v>347</v>
-      </c>
       <c r="R82" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S82" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T82" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U82" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V82" s="40">
         <v>0</v>
       </c>
       <c r="W82" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X82" s="32">
         <v>0.25</v>
@@ -10821,7 +10810,7 @@
         <v>5</v>
       </c>
       <c r="Z82" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA82" s="32">
         <v>8</v>
@@ -10845,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="AH82" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="83" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -10868,16 +10857,16 @@
         <v>169</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="I83" s="8" t="s">
         <v>178</v>
       </c>
       <c r="J83" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K83" s="8" t="s">
         <v>168</v>
@@ -10886,37 +10875,37 @@
         <v>174</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N83" s="7" t="s">
         <v>169</v>
       </c>
       <c r="O83" s="24" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="P83" s="25" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Q83" s="29" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R83" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S83" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T83" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="U83" s="25" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="V83" s="40">
         <v>60</v>
       </c>
       <c r="W83" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="X83" s="32">
         <v>0.02</v>
@@ -10925,7 +10914,7 @@
         <v>5</v>
       </c>
       <c r="Z83" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA83" s="32">
         <v>6</v>
@@ -10934,7 +10923,7 @@
         <v>50</v>
       </c>
       <c r="AC83" s="25" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AD83" s="32">
         <v>0</v>
@@ -10949,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AH83" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="84" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="6">
         <v>83</v>
       </c>
@@ -10975,13 +10964,13 @@
         <v>180</v>
       </c>
       <c r="H84" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I84" s="5" t="s">
         <v>178</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K84" s="5" t="s">
         <v>163</v>
@@ -10990,31 +10979,31 @@
         <v>164</v>
       </c>
       <c r="M84" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N84" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O84" s="24" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="P84" s="25" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Q84" s="25" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="R84" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S84" s="25" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T84" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U84" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V84" s="40">
         <v>20</v>
@@ -11029,7 +11018,7 @@
         <v>12</v>
       </c>
       <c r="Z84" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA84" s="32">
         <v>27</v>
@@ -11056,7 +11045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -11085,7 +11074,7 @@
         <v>178</v>
       </c>
       <c r="J85" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K85" s="8" t="s">
         <v>173</v>
@@ -11094,31 +11083,31 @@
         <v>174</v>
       </c>
       <c r="M85" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="N85" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="N85" s="7" t="s">
-        <v>320</v>
-      </c>
       <c r="O85" s="24" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P85" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="Q85" s="25" t="s">
-        <v>435</v>
+        <v>432</v>
+      </c>
+      <c r="Q85" s="29" t="s">
+        <v>402</v>
       </c>
       <c r="R85" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S85" s="25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="T85" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U85" s="25" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="V85" s="40">
         <v>282</v>
@@ -11133,7 +11122,7 @@
         <v>300</v>
       </c>
       <c r="Z85" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA85" s="32">
         <v>16</v>
@@ -11142,25 +11131,25 @@
         <v>42.5</v>
       </c>
       <c r="AC85" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AD85" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AE85" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF85" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG85" s="32">
         <v>1</v>
       </c>
       <c r="AH85" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="86" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -11189,7 +11178,7 @@
         <v>178</v>
       </c>
       <c r="J86" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K86" s="5" t="s">
         <v>173</v>
@@ -11198,31 +11187,31 @@
         <v>164</v>
       </c>
       <c r="M86" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N86" s="4" t="s">
         <v>188</v>
       </c>
       <c r="O86" s="28" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="P86" s="29" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="Q86" s="29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="R86" s="29" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S86" s="29" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="T86" s="28" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U86" s="29" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V86" s="41">
         <v>170</v>
@@ -11237,7 +11226,7 @@
         <v>10</v>
       </c>
       <c r="Z86" s="29" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA86" s="33">
         <v>10</v>
@@ -11261,10 +11250,10 @@
         <v>0</v>
       </c>
       <c r="AH86" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
-    <row r="87" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="6">
         <v>86</v>
       </c>
@@ -11287,13 +11276,13 @@
         <v>170</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>161</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K87" s="5" t="s">
         <v>163</v>
@@ -11302,31 +11291,31 @@
         <v>164</v>
       </c>
       <c r="M87" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N87" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O87" s="24" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="P87" s="25" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="Q87" s="25" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R87" s="25" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="S87" s="25" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="T87" s="24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="U87" s="25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="V87" s="40">
         <v>132</v>
@@ -11341,7 +11330,7 @@
         <v>45</v>
       </c>
       <c r="Z87" s="25" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AA87" s="32">
         <v>18</v>
@@ -11368,7 +11357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:34" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:34" ht="31.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="6">
         <v>87</v>
       </c>
@@ -11397,7 +11386,7 @@
         <v>161</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K88" s="5" t="s">
         <v>173</v>
@@ -11406,31 +11395,31 @@
         <v>174</v>
       </c>
       <c r="M88" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N88" s="4" t="s">
         <v>169</v>
       </c>
       <c r="O88" s="24" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="P88" s="25" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Q88" s="29" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R88" s="25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="S88" s="25" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="T88" s="24" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U88" s="25" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="V88" s="40">
         <v>0</v>
@@ -11445,7 +11434,7 @@
         <v>153</v>
       </c>
       <c r="Z88" s="25" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA88" s="32">
         <v>80</v>
@@ -11454,26 +11443,32 @@
         <v>90</v>
       </c>
       <c r="AC88" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AD88" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AE88" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF88" s="25" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AG88" s="25" t="s">
         <v>164</v>
       </c>
       <c r="AH88" s="29" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AH88" xr:uid="{2F761443-1744-4535-9313-0EB188E919B2}"/>
+  <autoFilter ref="A1:AH88" xr:uid="{2F761443-1744-4535-9313-0EB188E919B2}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="TRL: 9 for LAM-DED technology and TRL:4 for Micro 3D Printing"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
